--- a/test_data/WTA/WTA Pillar2 Regulation/WTA Pillar2 Regulation_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Regulation/WTA Pillar2 Regulation_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -561,17 +553,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Regulation did not show the expected placeholder/search box.</t>
+          <t>Pillar 2 &gt; Regulation loaded with the placeholder and Search box visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Placeholder and Search box are visible</t>
+          <t>[PASS] Placeholder and Search box are visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -628,7 +620,7 @@
           <t>[PASS] Regulations table with 'Entry into Force' column is visible</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -686,7 +678,7 @@
           <t>[PASS] An 'Add to Project' button is present on a regulation row</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -745,7 +737,67 @@
           <t>[PASS] Search box holds the typed value</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P2Reg_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Regulation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>The 'Download' column's link triggers a real, non-empty file download</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the regulation row's 'English' download link must trigger a real download with no failure and a non-zero size - this module previously had no download coverage at all, only the 'Download' column heading was referenced in a docstring.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Pillar 2 &gt; Regulation.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Pillar 2 &gt; Regulation
+2. Select Australia
+3. Click the 'English' download link
+4. Verify a real, non-empty file download completed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the regulation row's 'English' download link must trigger a real download with no failure and a non-zero size - this module previously had no download coverage at all, only the 'Download' column heading was referenced in a docstring.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>The download link correctly downloaded 'AU_Section_102_15_of_the__ITAA_1997_English_pdf.pdf' (82803 bytes).</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The 'English' download link produces a real, non-empty file with no failure</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 Regulation/WTA Pillar2 Regulation_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Regulation/WTA Pillar2 Regulation_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Reg_01</t>
+          <t>P2Reg_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,55 +530,55 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Regulation loads with the jurisdiction placeholder</t>
+          <t>Each regulation row has an Add to Project button</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load showing the left-panel instruction text and a 'Search' box.</t>
+          <t>For Australia, at least one regulation row must show an 'Add to Project' button.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on Pillar 2 &gt; Regulation.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Pillar 2 &gt; Regulation
-2. Verify the placeholder text and Search box are visible</t>
+          <t>1. Log in, open Pillar 2 &gt; Regulation, select Australia
+2. Verify an 'Add to Project' button is visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must load showing the left-panel instruction text and a 'Search' box.</t>
+          <t>For Australia, at least one regulation row must show an 'Add to Project' button.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Regulation loaded with the placeholder and Search box visible.</t>
+          <t>A regulation row was missing its 'Add to Project' action.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Placeholder and Search box are visible</t>
+          <t>[FAIL] An 'Add to Project' button is present on a regulation row</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2Reg_02</t>
+          <t>P2Reg_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,12 +588,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction renders the regulations table</t>
+          <t>The regulations Search box accepts free-text input</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render a 'Showing regulations of Australia' table with an 'Entry into Force' column.</t>
+          <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -595,209 +603,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>Search term: capital</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Regulation
-2. Check 'Australia'
-3. Verify the regulations table and its 'Entry into Force' column are visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' must render a 'Showing regulations of Australia' table with an 'Entry into Force' column.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia rendered the regulations table with the expected columns.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Regulations table with 'Entry into Force' column is visible</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2Reg_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Regulation</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Each regulation row has an Add to Project button</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia, at least one regulation row must show an 'Add to Project' button.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; Regulation.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Pillar 2 &gt; Regulation, select Australia
-2. Verify an 'Add to Project' button is visible</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia, at least one regulation row must show an 'Add to Project' button.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Each regulation row exposed an 'Add to Project' action.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] An 'Add to Project' button is present on a regulation row</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2Reg_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Regulation</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>The regulations Search box accepts free-text input</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Pillar 2 &gt; Regulation.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Search term: capital</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Regulation
 2. Type 'capital' into the Search box
 3. Verify the box holds the typed value</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>The Search box accepted and retained the typed value 'capital'.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] Search box holds the typed value</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P2Reg_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Regulation</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The 'Download' column's link triggers a real, non-empty file download</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the regulation row's 'English' download link must trigger a real download with no failure and a non-zero size - this module previously had no download coverage at all, only the 'Download' column heading was referenced in a docstring.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; Regulation.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Regulation
-2. Select Australia
-3. Click the 'English' download link
-4. Verify a real, non-empty file download completed</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the regulation row's 'English' download link must trigger a real download with no failure and a non-zero size - this module previously had no download coverage at all, only the 'Download' column heading was referenced in a docstring.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>The download link correctly downloaded 'AU_Section_102_15_of_the__ITAA_1997_English_pdf.pdf' (82803 bytes).</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The 'English' download link produces a real, non-empty file with no failure</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 Regulation/WTA Pillar2 Regulation_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Regulation/WTA Pillar2 Regulation_Test_Cases.xlsx
@@ -44,12 +44,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Reg_03</t>
+          <t>P2Reg_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -530,55 +530,55 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Each regulation row has an Add to Project button</t>
+          <t>Pillar 2 &gt; Regulation loads with the jurisdiction placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>For Australia, at least one regulation row must show an 'Add to Project' button.</t>
+          <t>The page must load showing the left-panel instruction text and a 'Search' box.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; Regulation.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open Pillar 2 &gt; Regulation, select Australia
-2. Verify an 'Add to Project' button is visible</t>
+          <t>1. Log in and open Pillar 2 &gt; Regulation
+2. Verify the placeholder text and Search box are visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>For Australia, at least one regulation row must show an 'Add to Project' button.</t>
+          <t>The page must load showing the left-panel instruction text and a 'Search' box.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>A regulation row was missing its 'Add to Project' action.</t>
+          <t>Pillar 2 &gt; Regulation loaded with the placeholder and Search box visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] An 'Add to Project' button is present on a regulation row</t>
+          <t>[PASS] Placeholder and Search box are visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2Reg_04</t>
+          <t>P2Reg_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The regulations Search box accepts free-text input</t>
+          <t>Selecting a jurisdiction renders the regulations table</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
+          <t>Checking 'Australia' must render a 'Showing regulations of Australia' table with an 'Entry into Force' column.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -603,34 +603,34 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Search term: capital</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Regulation
-2. Type 'capital' into the Search box
-3. Verify the box holds the typed value</t>
+2. Check 'Australia'
+3. Verify the regulations table and its 'Entry into Force' column are visible</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
+          <t>Checking 'Australia' must render a 'Showing regulations of Australia' table with an 'Entry into Force' column.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The Search box accepted and retained the typed value 'capital'.</t>
+          <t>The regulations table did not render as expected.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Search box holds the typed value</t>
+          <t>[FAIL] Regulations table with 'Entry into Force' column is visible</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
